--- a/exports/trend_1d/SYRMA_full_report.xlsx
+++ b/exports/trend_1d/SYRMA_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q27"/>
+  <dimension ref="A1:U27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,22 +557,22 @@
         <v>21.06</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44916</v>
+        <v>44917</v>
       </c>
       <c r="H2" t="n">
-        <v>276.95</v>
+        <v>268</v>
       </c>
       <c r="I2" t="n">
         <v>273.183292142329</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K2" t="n">
-        <v>-7.91</v>
+        <v>-10.89</v>
       </c>
       <c r="L2" t="n">
-        <v>10.72</v>
+        <v>12.39</v>
       </c>
       <c r="M2" t="n">
         <v>1.92</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>70</v>
+        <v>71</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>4</v>
+      </c>
+      <c r="U2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>13.07</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44979</v>
+        <v>44980</v>
       </c>
       <c r="H3" t="n">
-        <v>264.9</v>
+        <v>278.75</v>
       </c>
       <c r="I3" t="n">
         <v>277.2557216422953</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K3" t="n">
-        <v>1.16</v>
+        <v>-4.01</v>
       </c>
       <c r="L3" t="n">
         <v>6.34</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>13.18</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>45224</v>
+        <v>45225</v>
       </c>
       <c r="H4" t="n">
-        <v>593.2</v>
+        <v>578.75</v>
       </c>
       <c r="I4" t="n">
         <v>582.6768916742974</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="K4" t="n">
-        <v>112.81</v>
+        <v>107.62</v>
       </c>
       <c r="L4" t="n">
         <v>10.1</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>164</v>
+        <v>165</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>8</v>
+      </c>
+      <c r="U4" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>15.12</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="H5" t="n">
-        <v>590.3</v>
+        <v>607.95</v>
       </c>
       <c r="I5" t="n">
         <v>595.9121534128537</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K5" t="n">
-        <v>-2</v>
+        <v>-5.05</v>
       </c>
       <c r="L5" t="n">
         <v>10.15</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>10.99</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>45296</v>
+        <v>45299</v>
       </c>
       <c r="H6" t="n">
-        <v>631.2</v>
+        <v>609.05</v>
       </c>
       <c r="I6" t="n">
         <v>619.8163745648027</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K6" t="n">
-        <v>3.82</v>
+        <v>0.18</v>
       </c>
       <c r="L6" t="n">
         <v>2.47</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>12.81</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>45435</v>
+        <v>45436</v>
       </c>
       <c r="H7" t="n">
-        <v>452.05</v>
+        <v>478.7</v>
       </c>
       <c r="I7" t="n">
         <v>457.2723826921069</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="K7" t="n">
-        <v>25.78</v>
+        <v>21.4</v>
       </c>
       <c r="L7" t="n">
         <v>4.26</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>93</v>
+        <v>94</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>5</v>
+      </c>
+      <c r="U7" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -876,25 +971,25 @@
         <v>16.02</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="H8" t="n">
-        <v>466.3</v>
+        <v>427.75</v>
       </c>
       <c r="I8" t="n">
         <v>450.189367342276</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K8" t="n">
-        <v>-2.59</v>
+        <v>-10.64</v>
       </c>
       <c r="L8" t="n">
         <v>14.03</v>
       </c>
       <c r="M8" t="n">
-        <v>2.88</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="N8" t="n">
         <v>9.949999999999999</v>
@@ -906,7 +1001,19 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>4</v>
+      </c>
+      <c r="U8" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -933,28 +1040,28 @@
         <v>17.71</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="H9" t="n">
-        <v>419.6</v>
+        <v>463.75</v>
       </c>
       <c r="I9" t="n">
         <v>455.5875594252958</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K9" t="n">
-        <v>1.91</v>
+        <v>-8.42</v>
       </c>
       <c r="L9" t="n">
-        <v>8.23</v>
+        <v>10.93</v>
       </c>
       <c r="M9" t="n">
         <v>2.18</v>
       </c>
       <c r="N9" t="n">
-        <v>3.45</v>
+        <v>10.52</v>
       </c>
       <c r="O9" t="n">
         <v>-8.27</v>
@@ -963,7 +1070,19 @@
         <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,22 +1109,22 @@
         <v>14.08</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>45569</v>
+        <v>45572</v>
       </c>
       <c r="H10" t="n">
-        <v>416</v>
+        <v>408.95</v>
       </c>
       <c r="I10" t="n">
         <v>415.2941431402446</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K10" t="n">
-        <v>-10.3</v>
+        <v>-11.82</v>
       </c>
       <c r="L10" t="n">
-        <v>10.65</v>
+        <v>13.6</v>
       </c>
       <c r="M10" t="n">
         <v>1.97</v>
@@ -1020,7 +1139,19 @@
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1047,28 +1178,28 @@
         <v>12.6</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>45590</v>
+        <v>45593</v>
       </c>
       <c r="H11" t="n">
-        <v>379.55</v>
+        <v>432.15</v>
       </c>
       <c r="I11" t="n">
         <v>427.4060392377737</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K11" t="n">
-        <v>7.19</v>
+        <v>-5.67</v>
       </c>
       <c r="L11" t="n">
-        <v>3.04</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="M11" t="n">
-        <v>1.5</v>
+        <v>2.63</v>
       </c>
       <c r="N11" t="n">
-        <v>1.03</v>
+        <v>13.86</v>
       </c>
       <c r="O11" t="n">
         <v>-1.69</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S11" t="b">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>16.52</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>45667</v>
+        <v>45670</v>
       </c>
       <c r="H12" t="n">
-        <v>567.8</v>
+        <v>529.4</v>
       </c>
       <c r="I12" t="n">
         <v>551.9885709484555</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="K12" t="n">
-        <v>31.39</v>
+        <v>22.5</v>
       </c>
       <c r="L12" t="n">
         <v>10.71</v>
@@ -1125,7 +1268,7 @@
         <v>3.1</v>
       </c>
       <c r="N12" t="n">
-        <v>5.15</v>
+        <v>6.76</v>
       </c>
       <c r="O12" t="n">
         <v>13.86</v>
@@ -1134,7 +1277,19 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>4</v>
+      </c>
+      <c r="U12" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>24.11</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>45686</v>
+        <v>45687</v>
       </c>
       <c r="H13" t="n">
-        <v>505.1</v>
+        <v>536.1</v>
       </c>
       <c r="I13" t="n">
         <v>518.9180349882107</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K13" t="n">
-        <v>4.59</v>
+        <v>-1.27</v>
       </c>
       <c r="L13" t="n">
         <v>11.22</v>
@@ -1191,7 +1346,19 @@
         <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S13" t="b">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1218,22 +1385,22 @@
         <v>22.4</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>45701</v>
+        <v>45702</v>
       </c>
       <c r="H14" t="n">
-        <v>466.75</v>
+        <v>441.55</v>
       </c>
       <c r="I14" t="n">
         <v>452.5748625928303</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K14" t="n">
-        <v>-12.94</v>
+        <v>-17.64</v>
       </c>
       <c r="L14" t="n">
-        <v>15.44</v>
+        <v>18.49</v>
       </c>
       <c r="M14" t="n">
         <v>2.99</v>
@@ -1248,7 +1415,19 @@
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1275,22 +1454,22 @@
         <v>26.28</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>45740</v>
+        <v>45741</v>
       </c>
       <c r="H15" t="n">
-        <v>482.2</v>
+        <v>487.9</v>
       </c>
       <c r="I15" t="n">
         <v>486.5950246081301</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K15" t="n">
-        <v>-9.210000000000001</v>
+        <v>-10.5</v>
       </c>
       <c r="L15" t="n">
-        <v>10.16</v>
+        <v>11.55</v>
       </c>
       <c r="M15" t="n">
         <v>2.3</v>
@@ -1305,7 +1484,19 @@
         <v>1</v>
       </c>
       <c r="Q15" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>15.89</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>45880</v>
+        <v>45881</v>
       </c>
       <c r="H16" t="n">
-        <v>717.95</v>
+        <v>673.3</v>
       </c>
       <c r="I16" t="n">
         <v>677.5857421425228</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="K16" t="n">
-        <v>47.15</v>
+        <v>38</v>
       </c>
       <c r="L16" t="n">
         <v>24.16</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>95</v>
+        <v>96</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>6</v>
+      </c>
+      <c r="U16" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="17">
@@ -1389,28 +1592,28 @@
         <v>17.77</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>45903</v>
+        <v>45904</v>
       </c>
       <c r="H17" t="n">
-        <v>791.5</v>
+        <v>836.15</v>
       </c>
       <c r="I17" t="n">
         <v>792.969644256532</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K17" t="n">
-        <v>-17.56</v>
+        <v>-24.19</v>
       </c>
       <c r="L17" t="n">
-        <v>19.34</v>
+        <v>25.5</v>
       </c>
       <c r="M17" t="n">
         <v>2.36</v>
       </c>
       <c r="N17" t="n">
-        <v>4.1</v>
+        <v>5.64</v>
       </c>
       <c r="O17" t="n">
         <v>-6.22</v>
@@ -1419,7 +1622,19 @@
         <v>1</v>
       </c>
       <c r="Q17" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>14.08</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>45994</v>
+        <v>45995</v>
       </c>
       <c r="H18" t="n">
-        <v>795.35</v>
+        <v>786.25</v>
       </c>
       <c r="I18" t="n">
         <v>788.3068889148902</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K18" t="n">
-        <v>-4.88</v>
+        <v>-5.97</v>
       </c>
       <c r="L18" t="n">
         <v>11.15</v>
@@ -1476,7 +1691,19 @@
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>4</v>
+      </c>
+      <c r="U18" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>13.2</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="H19" t="n">
-        <v>657.1</v>
+        <v>722.9</v>
       </c>
       <c r="I19" t="n">
         <v>721.2809480054389</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K19" t="n">
-        <v>16.43</v>
+        <v>8.06</v>
       </c>
       <c r="L19" t="n">
         <v>2</v>
@@ -1524,7 +1751,7 @@
         <v>2.23</v>
       </c>
       <c r="N19" t="n">
-        <v>4.28</v>
+        <v>10.01</v>
       </c>
       <c r="O19" t="n">
         <v>-1.14</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>16.04</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>46083</v>
+        <v>46085</v>
       </c>
       <c r="H20" t="n">
-        <v>781.35</v>
+        <v>738.85</v>
       </c>
       <c r="I20" t="n">
         <v>769.4267525450973</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="K20" t="n">
-        <v>8.09</v>
+        <v>2.21</v>
       </c>
       <c r="L20" t="n">
         <v>8.57</v>
@@ -1581,7 +1820,7 @@
         <v>5.22</v>
       </c>
       <c r="N20" t="n">
-        <v>4.97</v>
+        <v>5.44</v>
       </c>
       <c r="O20" t="n">
         <v>10.01</v>
@@ -1590,7 +1829,19 @@
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1617,22 +1868,22 @@
         <v>15.76</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="H21" t="n">
-        <v>808.45</v>
+        <v>844.6</v>
       </c>
       <c r="I21" t="n">
         <v>827.1584840650966</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K21" t="n">
-        <v>-9.42</v>
+        <v>-14.31</v>
       </c>
       <c r="L21" t="n">
-        <v>13.89</v>
+        <v>14.88</v>
       </c>
       <c r="M21" t="n">
         <v>4.76</v>
@@ -1647,7 +1898,19 @@
         <v>1</v>
       </c>
       <c r="Q21" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>14.06</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="H22" t="n">
-        <v>1013.25</v>
+        <v>969.95</v>
       </c>
       <c r="I22" t="n">
         <v>986.3709045431521</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="K22" t="n">
-        <v>19.97</v>
+        <v>14.84</v>
       </c>
       <c r="L22" t="n">
         <v>2.32</v>
@@ -1695,7 +1958,7 @@
         <v>2.14</v>
       </c>
       <c r="N22" t="n">
-        <v>3.68</v>
+        <v>4.27</v>
       </c>
       <c r="O22" t="n">
         <v>4.47</v>
@@ -1704,7 +1967,19 @@
         <v>1</v>
       </c>
       <c r="Q22" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,28 +2006,28 @@
         <v>17.97</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="H23" t="n">
-        <v>1107.3</v>
+        <v>1166.8</v>
       </c>
       <c r="I23" t="n">
         <v>1126.927615868683</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K23" t="n">
-        <v>-14.16</v>
+        <v>-20.29</v>
       </c>
       <c r="L23" t="n">
-        <v>14.95</v>
+        <v>21.04</v>
       </c>
       <c r="M23" t="n">
         <v>1.59</v>
       </c>
       <c r="N23" t="n">
-        <v>3.3</v>
+        <v>5.37</v>
       </c>
       <c r="O23" t="n">
         <v>-4.27</v>
@@ -1761,7 +2036,19 @@
         <v>1</v>
       </c>
       <c r="Q23" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>14.67</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="H24" t="n">
-        <v>1380</v>
+        <v>1288.3</v>
       </c>
       <c r="I24" t="n">
         <v>1303.695932881541</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K24" t="n">
-        <v>18.27</v>
+        <v>10.41</v>
       </c>
       <c r="L24" t="n">
         <v>5.98</v>
@@ -1809,7 +2096,7 @@
         <v>2.67</v>
       </c>
       <c r="N24" t="n">
-        <v>5.01</v>
+        <v>6.64</v>
       </c>
       <c r="O24" t="n">
         <v>5.37</v>
@@ -1818,7 +2105,19 @@
         <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1845,28 +2144,28 @@
         <v>15.44</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="H25" t="n">
-        <v>1424.7</v>
+        <v>1516.4</v>
       </c>
       <c r="I25" t="n">
         <v>1456.676883287854</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K25" t="n">
-        <v>-10.59</v>
+        <v>-17.71</v>
       </c>
       <c r="L25" t="n">
-        <v>13.95</v>
+        <v>18.14</v>
       </c>
       <c r="M25" t="n">
         <v>2.65</v>
       </c>
       <c r="N25" t="n">
-        <v>4.48</v>
+        <v>6.44</v>
       </c>
       <c r="O25" t="n">
         <v>-6.64</v>
@@ -1875,7 +2174,19 @@
         <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>14.29</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>46314</v>
+        <v>46316</v>
       </c>
       <c r="H26" t="n">
-        <v>1547.6</v>
+        <v>1473.1</v>
       </c>
       <c r="I26" t="n">
         <v>1539.204100566945</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="K26" t="n">
-        <v>2.06</v>
+        <v>-2.86</v>
       </c>
       <c r="L26" t="n">
         <v>8.16</v>
@@ -1932,7 +2243,19 @@
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>3</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -1983,6 +2306,14 @@
       <c r="Q27" t="n">
         <v>6</v>
       </c>
+      <c r="R27" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3847,7 +4178,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>58.4</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6">
@@ -3857,7 +4188,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7">
@@ -3867,7 +4198,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="8">
@@ -3877,7 +4208,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
@@ -3887,7 +4218,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="10">
@@ -3897,7 +4228,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>121.6</v>
+        <v>122.6</v>
       </c>
     </row>
     <row r="11">
@@ -3907,7 +4238,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
@@ -3917,7 +4248,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13">
@@ -3927,7 +4258,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="14">
@@ -3937,7 +4268,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>7.96</v>
+        <v>2.16</v>
       </c>
     </row>
     <row r="15">
@@ -3947,7 +4278,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>15.76</v>
+        <v>10.46</v>
       </c>
     </row>
     <row r="16">
@@ -3957,7 +4288,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.49</v>
+        <v>-6.83</v>
       </c>
     </row>
     <row r="17">
@@ -3967,7 +4298,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>112.81</v>
+        <v>107.62</v>
       </c>
     </row>
     <row r="18">
@@ -3977,7 +4308,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>56</v>
+        <v>36</v>
       </c>
     </row>
     <row r="19">
@@ -3987,7 +4318,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>10.08</v>
+        <v>11.45</v>
       </c>
     </row>
     <row r="20">
@@ -3997,7 +4328,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>10.16</v>
+        <v>10.93</v>
       </c>
     </row>
     <row r="21">
@@ -4007,7 +4338,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>24.16</v>
+        <v>25.5</v>
       </c>
     </row>
     <row r="22">
@@ -4017,7 +4348,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23">
@@ -4027,7 +4358,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="24">
@@ -4037,7 +4368,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3.35</v>
+        <v>3.65</v>
       </c>
     </row>
     <row r="25">
@@ -4057,7 +4388,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>5.61</v>
+        <v>7.03</v>
       </c>
     </row>
     <row r="27">
@@ -4077,7 +4408,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="29">
